--- a/1. List_ManualData.xlsx
+++ b/1. List_ManualData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/Stocks/Data/Stocks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B59270-376F-E246-A6E9-C6D750AFCABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/1. List_ManualData.xlsx
+++ b/1. List_ManualData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B59270-376F-E246-A6E9-C6D750AFCABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A301187F-1750-2341-A3AC-63775B976B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="100" windowWidth="25440" windowHeight="13540" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Name</t>
   </si>
@@ -63,13 +63,19 @@
   </si>
   <si>
     <t>NASDAQ</t>
+  </si>
+  <si>
+    <t>Market eisk premiums:</t>
+  </si>
+  <si>
+    <t>USA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -82,6 +88,13 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -126,18 +139,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -517,11 +533,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B2:F6"/>
+  <dimension ref="B2:F12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" style="1"/>
     <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" style="1"/>
@@ -602,6 +618,27 @@
         <v>0.86</v>
       </c>
     </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/1. List_ManualData.xlsx
+++ b/1. List_ManualData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A301187F-1750-2341-A3AC-63775B976B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390E81BB-E20A-8F43-87ED-D78A8317C4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="100" windowWidth="25440" windowHeight="13540" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -65,10 +65,10 @@
     <t>NASDAQ</t>
   </si>
   <si>
-    <t>Market eisk premiums:</t>
-  </si>
-  <si>
     <t>USA</t>
+  </si>
+  <si>
+    <t>Market risk premiums:</t>
   </si>
 </sst>
 </file>
@@ -572,16 +572,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="4">
-        <v>24.45</v>
+        <v>26.47</v>
       </c>
       <c r="D4" s="4">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="E4" s="4">
-        <v>22.1</v>
+        <v>23.69</v>
       </c>
       <c r="F4" s="4">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
@@ -589,16 +589,16 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>23.55</v>
+        <v>24.16</v>
       </c>
       <c r="D5" s="4">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="E5" s="4">
-        <v>23.24</v>
+        <v>23.54</v>
       </c>
       <c r="F5" s="4">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.2">
@@ -606,21 +606,21 @@
         <v>8</v>
       </c>
       <c r="C6" s="4">
-        <v>30.87</v>
+        <v>35.590000000000003</v>
       </c>
       <c r="D6" s="4">
-        <v>0.65</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="E6" s="4">
-        <v>28.25</v>
+        <v>31.25</v>
       </c>
       <c r="F6" s="4">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.2">
@@ -633,10 +633,10 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>0.05</v>
+        <v>4.4999999999999998E-2</v>
       </c>
     </row>
   </sheetData>
